--- a/source/kaoqing/template/加班申请单模板.xlsx
+++ b/source/kaoqing/template/加班申请单模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\小红叔\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49BF368A-9A50-4506-87C9-D086F7A16B1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4131B732-1907-4201-9DBF-C29C7113DB22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="720" windowWidth="14610" windowHeight="15480" xr2:uid="{9E8CE971-05BC-4D55-8DB8-534D7FFB8A75}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9E8CE971-05BC-4D55-8DB8-534D7FFB8A75}"/>
   </bookViews>
   <sheets>
     <sheet name="template" sheetId="1" r:id="rId1"/>
@@ -743,7 +743,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
+  </numFmts>
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -840,6 +843,15 @@
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -964,7 +976,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -989,9 +1001,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -999,12 +1008,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1017,14 +1035,11 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1363,7 +1378,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="11.5" customWidth="1"/>
@@ -1376,15 +1391,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="37.5" customHeight="1">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" ht="39" customHeight="1">
       <c r="A2" s="6" t="s">
@@ -1393,164 +1408,83 @@
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
     </row>
     <row r="3" spans="1:7" ht="24" customHeight="1">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="20" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="24" customHeight="1">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="21" t="s">
         <v>39</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="24" customHeight="1">
-      <c r="A5" s="7"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="7"/>
-    </row>
-    <row r="6" spans="1:7" ht="24" customHeight="1">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="7"/>
-    </row>
-    <row r="7" spans="1:7" ht="24" customHeight="1">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="7"/>
-    </row>
-    <row r="8" spans="1:7" ht="24" customHeight="1">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="7"/>
-    </row>
-    <row r="9" spans="1:7" ht="24" customHeight="1">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="7"/>
-    </row>
-    <row r="10" spans="1:7" ht="24" customHeight="1">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="7"/>
-    </row>
-    <row r="11" spans="1:7" ht="24" customHeight="1">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="7"/>
-    </row>
-    <row r="12" spans="1:7" ht="24" customHeight="1">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="7"/>
-    </row>
-    <row r="13" spans="1:7" ht="24" customHeight="1">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="7"/>
-    </row>
-    <row r="14" spans="1:7" ht="18">
-      <c r="A14" s="6" t="s">
+    <row r="5" spans="1:7" ht="18">
+      <c r="A5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-    </row>
-    <row r="15" spans="1:7" ht="42.75" customHeight="1">
-      <c r="A15" s="11" t="s">
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+    </row>
+    <row r="6" spans="1:7" ht="42.75" customHeight="1">
+      <c r="A6" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11" t="s">
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11" t="s">
+      <c r="E6" s="10"/>
+      <c r="F6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G15" s="11"/>
+      <c r="G6" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1574,18 +1508,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="3" t="s">
@@ -1749,11 +1683,11 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
     </row>
     <row r="20" spans="1:3" ht="17.25" thickBot="1">
       <c r="A20" s="3" t="s">
@@ -1820,11 +1754,11 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A28" s="14" t="s">
+      <c r="A28" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
     </row>
     <row r="29" spans="1:3" ht="17.25" thickBot="1">
       <c r="A29" s="3" t="s">
@@ -1914,38 +1848,38 @@
       <c r="C37" s="2"/>
     </row>
     <row r="38" spans="1:3" ht="39" customHeight="1">
-      <c r="A38" s="19" t="s">
+      <c r="A38" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="B38" s="20"/>
-      <c r="C38" s="20"/>
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
         <v>1</v>
       </c>
-      <c r="B39" s="18" t="s">
+      <c r="B39" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="C39" s="18"/>
+      <c r="C39" s="15"/>
     </row>
     <row r="40" spans="1:3" ht="48" customHeight="1">
       <c r="A40">
         <v>2</v>
       </c>
-      <c r="B40" s="18" t="s">
+      <c r="B40" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="C40" s="18"/>
+      <c r="C40" s="15"/>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
         <v>3</v>
       </c>
-      <c r="B41" s="18" t="s">
+      <c r="B41" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="C41" s="18"/>
+      <c r="C41" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/source/kaoqing/template/加班申请单模板.xlsx
+++ b/source/kaoqing/template/加班申请单模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\小红叔\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4131B732-1907-4201-9DBF-C29C7113DB22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22FB966F-D9AE-4614-B239-1EB1577CE025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9E8CE971-05BC-4D55-8DB8-534D7FFB8A75}"/>
+    <workbookView xWindow="1170" yWindow="720" windowWidth="14610" windowHeight="15480" xr2:uid="{9E8CE971-05BC-4D55-8DB8-534D7FFB8A75}"/>
   </bookViews>
   <sheets>
     <sheet name="template" sheetId="1" r:id="rId1"/>
@@ -814,15 +814,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -852,6 +843,14 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -995,29 +994,35 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1034,12 +1039,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1056,6 +1055,71 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>701432</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>885824</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>95249</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFF167E6-1E7F-FBBB-453C-57C280751EDE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6187832" y="1838325"/>
+          <a:ext cx="1051167" cy="609599"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1391,15 +1455,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="37.5" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:7" ht="39" customHeight="1">
       <c r="A2" s="6" t="s">
@@ -1408,32 +1472,32 @@
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:7" ht="24" customHeight="1">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="G3" s="13" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1447,7 +1511,7 @@
       <c r="C4" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="14" t="s">
         <v>39</v>
       </c>
       <c r="E4" s="7" t="s">
@@ -1494,6 +1558,7 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="11" scale="92" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1508,18 +1573,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="3" t="s">
@@ -1683,11 +1748,11 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
     </row>
     <row r="20" spans="1:3" ht="17.25" thickBot="1">
       <c r="A20" s="3" t="s">
@@ -1754,11 +1819,11 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A28" s="16" t="s">
+      <c r="A28" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
     </row>
     <row r="29" spans="1:3" ht="17.25" thickBot="1">
       <c r="A29" s="3" t="s">
@@ -1858,28 +1923,28 @@
       <c r="A39">
         <v>1</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="B39" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C39" s="15"/>
+      <c r="C39" s="17"/>
     </row>
     <row r="40" spans="1:3" ht="48" customHeight="1">
       <c r="A40">
         <v>2</v>
       </c>
-      <c r="B40" s="15" t="s">
+      <c r="B40" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="C40" s="15"/>
+      <c r="C40" s="17"/>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
         <v>3</v>
       </c>
-      <c r="B41" s="15" t="s">
+      <c r="B41" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="C41" s="15"/>
+      <c r="C41" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/source/kaoqing/template/加班申请单模板.xlsx
+++ b/source/kaoqing/template/加班申请单模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\小红叔\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22FB966F-D9AE-4614-B239-1EB1577CE025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86E0B57-0B7E-4D61-A26A-A4866329B5FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="720" windowWidth="14610" windowHeight="15480" xr2:uid="{9E8CE971-05BC-4D55-8DB8-534D7FFB8A75}"/>
+    <workbookView xWindow="1950" yWindow="720" windowWidth="14610" windowHeight="15480" xr2:uid="{9E8CE971-05BC-4D55-8DB8-534D7FFB8A75}"/>
   </bookViews>
   <sheets>
     <sheet name="template" sheetId="1" r:id="rId1"/>
@@ -867,7 +867,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -969,13 +969,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -993,9 +1002,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1039,6 +1045,18 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1061,23 +1079,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>701432</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>885824</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>95249</xdr:rowOff>
+      <xdr:colOff>895467</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>523875</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="图片 2">
+        <xdr:cNvPr id="2" name="图片 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFF167E6-1E7F-FBBB-453C-57C280751EDE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{367EBF56-ADFF-B078-E556-5C4A8E63C593}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1085,32 +1103,17 @@
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:clrChange>
-            <a:clrFrom>
-              <a:srgbClr val="FFFFFF"/>
-            </a:clrFrom>
-            <a:clrTo>
-              <a:srgbClr val="FFFFFF">
-                <a:alpha val="0"/>
-              </a:srgbClr>
-            </a:clrTo>
-          </a:clrChange>
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect t="19606" b="3935"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6187832" y="1838325"/>
-          <a:ext cx="1051167" cy="609599"/>
+          <a:off x="6410325" y="1962150"/>
+          <a:ext cx="838317" cy="371475"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1455,105 +1458,109 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="37.5" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" ht="39" customHeight="1">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="15" t="s">
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" ht="24" customHeight="1">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="12" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="24" customHeight="1">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="8" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
     </row>
     <row r="6" spans="1:7" ht="42.75" customHeight="1">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10" t="s">
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10" t="s">
+      <c r="E6" s="24"/>
+      <c r="F6" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="10"/>
+      <c r="G6" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="6">
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:E6"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -1573,18 +1580,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="3" t="s">
@@ -1748,11 +1755,11 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
     </row>
     <row r="20" spans="1:3" ht="17.25" thickBot="1">
       <c r="A20" s="3" t="s">
@@ -1819,11 +1826,11 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A28" s="18" t="s">
+      <c r="A28" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
     </row>
     <row r="29" spans="1:3" ht="17.25" thickBot="1">
       <c r="A29" s="3" t="s">
@@ -1913,38 +1920,38 @@
       <c r="C37" s="2"/>
     </row>
     <row r="38" spans="1:3" ht="39" customHeight="1">
-      <c r="A38" s="11" t="s">
+      <c r="A38" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="B38" s="12"/>
-      <c r="C38" s="12"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
         <v>1</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C39" s="17"/>
+      <c r="C39" s="16"/>
     </row>
     <row r="40" spans="1:3" ht="48" customHeight="1">
       <c r="A40">
         <v>2</v>
       </c>
-      <c r="B40" s="17" t="s">
+      <c r="B40" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C40" s="17"/>
+      <c r="C40" s="16"/>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
         <v>3</v>
       </c>
-      <c r="B41" s="17" t="s">
+      <c r="B41" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="C41" s="17"/>
+      <c r="C41" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/source/kaoqing/template/加班申请单模板.xlsx
+++ b/source/kaoqing/template/加班申请单模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\小红叔\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86E0B57-0B7E-4D61-A26A-A4866329B5FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D08A852-9F40-49DA-BDB1-D069D9D858D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="720" windowWidth="14610" windowHeight="15480" xr2:uid="{9E8CE971-05BC-4D55-8DB8-534D7FFB8A75}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="14610" windowHeight="15480" xr2:uid="{9E8CE971-05BC-4D55-8DB8-534D7FFB8A75}"/>
   </bookViews>
   <sheets>
     <sheet name="template" sheetId="1" r:id="rId1"/>
@@ -37,6 +37,28 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1025,12 +1047,24 @@
     <xf numFmtId="176" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1045,18 +1079,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1075,54 +1097,68 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>895467</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>523875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{367EBF56-ADFF-B078-E556-5C4A8E63C593}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:srcRect t="19606" b="3935"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6410325" y="1962150"/>
-          <a:ext cx="838317" cy="371475"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1449,8 +1485,7 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="11.5" customWidth="1"/>
-    <col min="2" max="2" width="14.375" customWidth="1"/>
-    <col min="3" max="3" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="15.625" customWidth="1"/>
     <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.25" customWidth="1"/>
     <col min="6" max="6" width="11.375" bestFit="1" customWidth="1"/>
@@ -1458,28 +1493,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="37.5" customHeight="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:7" ht="39" customHeight="1">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="14" t="s">
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:7" ht="24" customHeight="1">
       <c r="A3" s="12" t="s">
@@ -1528,30 +1563,32 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="18">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-    </row>
-    <row r="6" spans="1:7" ht="42.75" customHeight="1">
-      <c r="A6" s="24" t="s">
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+    </row>
+    <row r="6" spans="1:7" ht="35.25" customHeight="1">
+      <c r="A6" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24" t="s">
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="24"/>
-      <c r="F6" s="23" t="s">
+      <c r="E6" s="19"/>
+      <c r="F6" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="9"/>
+      <c r="G6" s="9" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1564,8 +1601,7 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="11" scale="92" orientation="landscape" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup paperSize="11" scale="82" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1580,18 +1616,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="3" t="s">
@@ -1755,11 +1791,11 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
     </row>
     <row r="20" spans="1:3" ht="17.25" thickBot="1">
       <c r="A20" s="3" t="s">
@@ -1826,11 +1862,11 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
     </row>
     <row r="29" spans="1:3" ht="17.25" thickBot="1">
       <c r="A29" s="3" t="s">
@@ -1930,28 +1966,28 @@
       <c r="A39">
         <v>1</v>
       </c>
-      <c r="B39" s="16" t="s">
+      <c r="B39" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="C39" s="16"/>
+      <c r="C39" s="20"/>
     </row>
     <row r="40" spans="1:3" ht="48" customHeight="1">
       <c r="A40">
         <v>2</v>
       </c>
-      <c r="B40" s="16" t="s">
+      <c r="B40" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="C40" s="16"/>
+      <c r="C40" s="20"/>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
         <v>3</v>
       </c>
-      <c r="B41" s="16" t="s">
+      <c r="B41" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="C41" s="16"/>
+      <c r="C41" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/source/kaoqing/template/加班申请单模板.xlsx
+++ b/source/kaoqing/template/加班申请单模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\小红叔\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D08A852-9F40-49DA-BDB1-D069D9D858D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AFE4675-34A7-4942-A354-3BB8017EDF74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="14610" windowHeight="15480" xr2:uid="{9E8CE971-05BC-4D55-8DB8-534D7FFB8A75}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9E8CE971-05BC-4D55-8DB8-534D7FFB8A75}"/>
   </bookViews>
   <sheets>
     <sheet name="template" sheetId="1" r:id="rId1"/>
@@ -39,30 +39,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="107">
   <si>
     <t>加班申请单</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -758,6 +736,106 @@
   </si>
   <si>
     <t>部门：{{{一级部门}}}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{签名}}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>对应人员的签名，签名图片文件为.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>\names</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>下对应姓名的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>jpg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>文件</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>也可指定人员，如</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>{{{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>顾晓维</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>}}}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{{顾晓维}}}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -768,7 +846,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -872,6 +950,20 @@
       <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1006,7 +1098,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1050,6 +1142,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1060,7 +1153,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1079,6 +1172,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1095,70 +1194,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1487,36 +1522,36 @@
     <col min="1" max="1" width="11.5" customWidth="1"/>
     <col min="2" max="3" width="15.625" customWidth="1"/>
     <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.25" customWidth="1"/>
-    <col min="6" max="6" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.875" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="37.5" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" ht="39" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="15" t="s">
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-    </row>
-    <row r="3" spans="1:7" ht="24" customHeight="1">
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+    </row>
+    <row r="3" spans="1:7" ht="26.1" customHeight="1">
       <c r="A3" s="12" t="s">
         <v>1</v>
       </c>
@@ -1539,7 +1574,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="24" customHeight="1">
+    <row r="4" spans="1:7" ht="26.1" customHeight="1">
       <c r="A4" s="8" t="s">
         <v>21</v>
       </c>
@@ -1562,32 +1597,32 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="18">
-      <c r="A5" s="18" t="s">
+    <row r="5" spans="1:7" s="15" customFormat="1" ht="26.1" customHeight="1">
+      <c r="A5" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-    </row>
-    <row r="6" spans="1:7" ht="35.25" customHeight="1">
-      <c r="A6" s="19" t="s">
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+    </row>
+    <row r="6" spans="1:7" ht="50.25" customHeight="1">
+      <c r="A6" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19" t="s">
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="19"/>
+      <c r="E6" s="20"/>
       <c r="F6" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="9" t="e" vm="1">
-        <v>#VALUE!</v>
+      <c r="G6" s="9" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -1607,7 +1642,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{614DADB2-EB97-4A0E-BDF8-782DBB5752E1}">
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="11.625" bestFit="1" customWidth="1"/>
@@ -1616,18 +1651,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="3" t="s">
@@ -1791,11 +1826,11 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
     </row>
     <row r="20" spans="1:3" ht="17.25" thickBot="1">
       <c r="A20" s="3" t="s">
@@ -1862,11 +1897,11 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
     </row>
     <row r="29" spans="1:3" ht="17.25" thickBot="1">
       <c r="A29" s="3" t="s">
@@ -1955,45 +1990,56 @@
       </c>
       <c r="C37" s="2"/>
     </row>
-    <row r="38" spans="1:3" ht="39" customHeight="1">
-      <c r="A38" s="10" t="s">
+    <row r="38" spans="1:3" ht="33" customHeight="1" thickBot="1">
+      <c r="A38" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C38" s="27" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="39" customHeight="1">
+      <c r="A39" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="B38" s="11"/>
-      <c r="C38" s="11"/>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39">
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40">
         <v>1</v>
       </c>
-      <c r="B39" s="20" t="s">
+      <c r="B40" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="C39" s="20"/>
-    </row>
-    <row r="40" spans="1:3" ht="48" customHeight="1">
-      <c r="A40">
+      <c r="C40" s="21"/>
+    </row>
+    <row r="41" spans="1:3" ht="48" customHeight="1">
+      <c r="A41">
         <v>2</v>
       </c>
-      <c r="B40" s="20" t="s">
+      <c r="B41" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="C40" s="20"/>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41">
+      <c r="C41" s="21"/>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42">
         <v>3</v>
       </c>
-      <c r="B41" s="20" t="s">
+      <c r="B42" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="C41" s="20"/>
+      <c r="C42" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="B39:C39"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A3:C3"/>

--- a/source/kaoqing/template/加班申请单模板.xlsx
+++ b/source/kaoqing/template/加班申请单模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\小红叔\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AFE4675-34A7-4942-A354-3BB8017EDF74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA7850A6-FFE3-41BE-8303-04BD79AA48F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9E8CE971-05BC-4D55-8DB8-534D7FFB8A75}"/>
+    <workbookView xWindow="1950" yWindow="0" windowWidth="14610" windowHeight="15480" xr2:uid="{9E8CE971-05BC-4D55-8DB8-534D7FFB8A75}"/>
   </bookViews>
   <sheets>
     <sheet name="template" sheetId="1" r:id="rId1"/>
@@ -835,7 +835,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{{{顾晓维}}}</t>
+    <t>{{{登录名}}}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1143,6 +1143,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1172,12 +1178,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1528,28 +1528,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="37.5" customHeight="1">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:7" ht="39" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="16" t="s">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
     </row>
     <row r="3" spans="1:7" ht="26.1" customHeight="1">
       <c r="A3" s="12" t="s">
@@ -1598,26 +1598,26 @@
       </c>
     </row>
     <row r="5" spans="1:7" s="15" customFormat="1" ht="26.1" customHeight="1">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
     </row>
     <row r="6" spans="1:7" ht="50.25" customHeight="1">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20" t="s">
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="20"/>
+      <c r="E6" s="22"/>
       <c r="F6" s="14" t="s">
         <v>10</v>
       </c>
@@ -1651,18 +1651,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="3" t="s">
@@ -1826,11 +1826,11 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A19" s="22" t="s">
+      <c r="A19" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
     </row>
     <row r="20" spans="1:3" ht="17.25" thickBot="1">
       <c r="A20" s="3" t="s">
@@ -1897,11 +1897,11 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A28" s="22" t="s">
+      <c r="A28" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B28" s="22"/>
-      <c r="C28" s="22"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
     </row>
     <row r="29" spans="1:3" ht="17.25" thickBot="1">
       <c r="A29" s="3" t="s">
@@ -1991,13 +1991,13 @@
       <c r="C37" s="2"/>
     </row>
     <row r="38" spans="1:3" ht="33" customHeight="1" thickBot="1">
-      <c r="A38" s="26" t="s">
+      <c r="A38" s="16" t="s">
         <v>103</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C38" s="27" t="s">
+      <c r="C38" s="17" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2012,28 +2012,28 @@
       <c r="A40">
         <v>1</v>
       </c>
-      <c r="B40" s="21" t="s">
+      <c r="B40" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="C40" s="21"/>
+      <c r="C40" s="23"/>
     </row>
     <row r="41" spans="1:3" ht="48" customHeight="1">
       <c r="A41">
         <v>2</v>
       </c>
-      <c r="B41" s="21" t="s">
+      <c r="B41" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="C41" s="21"/>
+      <c r="C41" s="23"/>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
         <v>3</v>
       </c>
-      <c r="B42" s="21" t="s">
+      <c r="B42" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="C42" s="21"/>
+      <c r="C42" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/source/kaoqing/template/加班申请单模板.xlsx
+++ b/source/kaoqing/template/加班申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\小红叔\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA7850A6-FFE3-41BE-8303-04BD79AA48F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FB7A061-F8A4-44A2-8AAF-965F8D6BF70C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="0" windowWidth="14610" windowHeight="15480" xr2:uid="{9E8CE971-05BC-4D55-8DB8-534D7FFB8A75}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="113">
   <si>
     <t>加班申请单</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -744,6 +744,51 @@
   </si>
   <si>
     <r>
+      <t>{{{真实姓名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>}}}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>也可指定人员签名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{{考勤人}}}</t>
+  </si>
+  <si>
+    <t>{{{一级部门领导}}}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{{二级部门领导}}}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>记录对应人员的签名，</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>签名占位符（签名图片文件为.\names下对应姓名的jpg文件）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>设置里面考勤组的相应绑定人员</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{{{</t>
+    </r>
+    <r>
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
@@ -751,7 +796,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>对应人员的签名，签名图片文件为.</t>
+      <t>考勤人</t>
     </r>
     <r>
       <rPr>
@@ -760,82 +805,8 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>\names</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>下对应姓名的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>jpg</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>文件</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>也可指定人员，如</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>{{{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>顾晓维</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
       <t>}}}</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{{登录名}}}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1098,7 +1069,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1146,8 +1117,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1161,9 +1132,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1178,6 +1146,18 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1551,7 +1531,7 @@
       <c r="F2" s="18"/>
       <c r="G2" s="18"/>
     </row>
-    <row r="3" spans="1:7" ht="26.1" customHeight="1">
+    <row r="3" spans="1:7" ht="30" customHeight="1">
       <c r="A3" s="12" t="s">
         <v>1</v>
       </c>
@@ -1574,7 +1554,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="26.1" customHeight="1">
+    <row r="4" spans="1:7" ht="30" customHeight="1">
       <c r="A4" s="8" t="s">
         <v>21</v>
       </c>
@@ -1609,15 +1589,15 @@
       <c r="G5" s="21"/>
     </row>
     <row r="6" spans="1:7" ht="50.25" customHeight="1">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="22"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22" t="s">
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="22"/>
+      <c r="E6" s="9"/>
       <c r="F6" s="14" t="s">
         <v>10</v>
       </c>
@@ -1626,13 +1606,11 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="4">
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:E6"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -1642,27 +1620,27 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{614DADB2-EB97-4A0E-BDF8-782DBB5752E1}">
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.625" customWidth="1"/>
     <col min="3" max="3" width="41.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="3" t="s">
@@ -1826,11 +1804,11 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A19" s="24" t="s">
+      <c r="A19" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
     </row>
     <row r="20" spans="1:3" ht="17.25" thickBot="1">
       <c r="A20" s="3" t="s">
@@ -1897,11 +1875,11 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A28" s="24" t="s">
+      <c r="A28" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="B28" s="24"/>
-      <c r="C28" s="24"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="23"/>
     </row>
     <row r="29" spans="1:3" ht="17.25" thickBot="1">
       <c r="A29" s="3" t="s">
@@ -1990,60 +1968,102 @@
       </c>
       <c r="C37" s="2"/>
     </row>
-    <row r="38" spans="1:3" ht="33" customHeight="1" thickBot="1">
-      <c r="A38" s="16" t="s">
+    <row r="38" spans="1:3" ht="16.5">
+      <c r="A38" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="B38" s="23"/>
+      <c r="C38" s="23"/>
+    </row>
+    <row r="39" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A39" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B39" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="C39" s="28"/>
+    </row>
+    <row r="40" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A40" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="C38" s="17" t="s">
+      <c r="B40" s="30" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" ht="39" customHeight="1">
-      <c r="A39" s="10" t="s">
+      <c r="C40" s="27"/>
+    </row>
+    <row r="41" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A41" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="B41" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="C41" s="27"/>
+    </row>
+    <row r="42" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A42" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="B42" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="C42" s="27"/>
+    </row>
+    <row r="43" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A43" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="B43" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="C43" s="27"/>
+    </row>
+    <row r="44" spans="1:3" ht="39" customHeight="1">
+      <c r="A44" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40">
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45">
         <v>1</v>
       </c>
-      <c r="B40" s="23" t="s">
+      <c r="B45" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="C40" s="23"/>
-    </row>
-    <row r="41" spans="1:3" ht="48" customHeight="1">
-      <c r="A41">
+      <c r="C45" s="22"/>
+    </row>
+    <row r="46" spans="1:3" ht="48" customHeight="1">
+      <c r="A46">
         <v>2</v>
       </c>
-      <c r="B41" s="23" t="s">
+      <c r="B46" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="C41" s="23"/>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42">
+      <c r="C46" s="22"/>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47">
         <v>3</v>
       </c>
-      <c r="B42" s="23" t="s">
+      <c r="B47" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="C42" s="23"/>
+      <c r="C47" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
+  <mergeCells count="8">
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A38:C38"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/source/kaoqing/template/加班申请单模板.xlsx
+++ b/source/kaoqing/template/加班申请单模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\小红叔\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FB7A061-F8A4-44A2-8AAF-965F8D6BF70C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{260762A0-98B4-42B2-8628-616EA570D927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="0" windowWidth="14610" windowHeight="15480" xr2:uid="{9E8CE971-05BC-4D55-8DB8-534D7FFB8A75}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9E8CE971-05BC-4D55-8DB8-534D7FFB8A75}"/>
   </bookViews>
   <sheets>
     <sheet name="template" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="120">
   <si>
     <t>加班申请单</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -66,10 +66,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>自愿加班</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>备注：加班申请单应在加班前一天审批。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -211,602 +207,762 @@
     <t>待提交/待审核/待批准/已批准</t>
   </si>
   <si>
+    <t>显示类别</t>
+  </si>
+  <si>
+    <t>国假加班/双休加班/事假…</t>
+  </si>
+  <si>
+    <t>{{加班类型}}</t>
+  </si>
+  <si>
+    <t>国假/双休/平时</t>
+  </si>
+  <si>
+    <t>仅加班类有值，请假类为空</t>
+  </si>
+  <si>
+    <t>{{考勤组}}</t>
+  </si>
+  <si>
+    <t>人员所属考勤组</t>
+  </si>
+  <si>
+    <t>取首位人员的组（多人跨组时取第一人）</t>
+  </si>
+  <si>
+    <t>文档级（整张表只替换一次）</t>
+  </si>
+  <si>
+    <t>当天 YYYY-MM-DD</t>
+  </si>
+  <si>
+    <t>当前时间</t>
+  </si>
+  <si>
+    <t>本次导出记录数</t>
+  </si>
+  <si>
+    <t>工时合计</t>
+  </si>
+  <si>
+    <t>当前筛选的考勤组</t>
+  </si>
+  <si>
+    <t>当前类别</t>
+  </si>
+  <si>
+    <t>当前状态筛选</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>占位符清单（设计模板时用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>{{...}}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>包住）</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>姓名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>}}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单据号</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>}}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>日期</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>}}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>时段</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>}}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>小时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>}}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>说明</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>}}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>√</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>流水号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人员信息占位符</t>
+  </si>
+  <si>
+    <t>来源字段</t>
+  </si>
+  <si>
+    <t>{{工号}}</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>人员编号</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>多人记录用「、」连接全部姓名</t>
+  </si>
+  <si>
+    <t>{{性别}}</t>
+  </si>
+  <si>
+    <t>gender</t>
+  </si>
+  <si>
+    <t>{{手机号}}</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>{{一级部门}}</t>
+  </si>
+  <si>
+    <t>dept1</t>
+  </si>
+  <si>
+    <t>{{二级部门}}</t>
+  </si>
+  <si>
+    <t>dept2</t>
+  </si>
+  <si>
+    <t>group</t>
+  </si>
+  <si>
+    <t>{{权限}}</t>
+  </si>
+  <si>
+    <t>permission</t>
+  </si>
+  <si>
+    <t>行级占位符写成三个大括号{{{xxx}}}，就只取一次，作为文档级占位符</t>
+  </si>
+  <si>
+    <r>
+      <t>{{{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>打印日期}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>}}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{{{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>打印时间</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>}}}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{{{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>总条数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>}}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{{{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>总小时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>}}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{{{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>当前组别}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>}}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{{{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>当前类别</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>}}}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{{{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>当前状态</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>}}}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>多人记录的取舍：{{姓名}} 会列出全部人员，但工号/性别/部门这类字段只取第一位人员（拼成一串没意义）。请假/加班申请单通常是一人一单，不受影响。</t>
+  </si>
+  <si>
+    <t>注意：</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>记录存储里时间是以 {{时段}}（"08:30-17:00"）整体存的，{{开始}}/{{结束}} 自动解析；</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>填写日期：{{{打印日期}}}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>部门：{{{一级部门}}}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{签名}}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{{{真实姓名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>}}}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>也可指定人员签名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>记录对应人员的签名，</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>设置里面考勤组的相应绑定人员</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{{{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>考勤人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>}}}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人员/签名占位符（签名图片文件为.\names下对应姓名的jpg文件）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>签名占位符</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{{{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>考勤人签名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>}}}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{{{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>一级部门领导签名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>}}}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{{{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>二级部门领导签名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>}}}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{{{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>一级部门领导</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>}}}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{{{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>二级部门领导</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>}}}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>姓名文字</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{{考勤人签名}}}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>自愿</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>类别</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>}}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>{{类别}}</t>
-  </si>
-  <si>
-    <t>显示类别</t>
-  </si>
-  <si>
-    <t>国假加班/双休加班/事假…</t>
-  </si>
-  <si>
-    <t>{{加班类型}}</t>
-  </si>
-  <si>
-    <t>国假/双休/平时</t>
-  </si>
-  <si>
-    <t>仅加班类有值，请假类为空</t>
-  </si>
-  <si>
-    <t>{{考勤组}}</t>
-  </si>
-  <si>
-    <t>人员所属考勤组</t>
-  </si>
-  <si>
-    <t>取首位人员的组（多人跨组时取第一人）</t>
-  </si>
-  <si>
-    <t>文档级（整张表只替换一次）</t>
-  </si>
-  <si>
-    <t>当天 YYYY-MM-DD</t>
-  </si>
-  <si>
-    <t>当前时间</t>
-  </si>
-  <si>
-    <t>本次导出记录数</t>
-  </si>
-  <si>
-    <t>工时合计</t>
-  </si>
-  <si>
-    <t>当前筛选的考勤组</t>
-  </si>
-  <si>
-    <t>当前类别</t>
-  </si>
-  <si>
-    <t>当前状态筛选</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>占位符清单（设计模板时用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>{{...}}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>包住）</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>{{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>姓名</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>}}</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>{{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单据号</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>}}</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>{{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>日期</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>}}</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>{{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>时段</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>}}</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>{{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>小时</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>}}</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>{{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>说明</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>}}</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>√</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>流水号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>人员信息占位符</t>
-  </si>
-  <si>
-    <t>来源字段</t>
-  </si>
-  <si>
-    <t>{{工号}}</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>人员编号</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>多人记录用「、」连接全部姓名</t>
-  </si>
-  <si>
-    <t>{{性别}}</t>
-  </si>
-  <si>
-    <t>gender</t>
-  </si>
-  <si>
-    <t>{{手机号}}</t>
-  </si>
-  <si>
-    <t>phone</t>
-  </si>
-  <si>
-    <t>{{一级部门}}</t>
-  </si>
-  <si>
-    <t>dept1</t>
-  </si>
-  <si>
-    <t>{{二级部门}}</t>
-  </si>
-  <si>
-    <t>dept2</t>
-  </si>
-  <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>{{权限}}</t>
-  </si>
-  <si>
-    <t>permission</t>
-  </si>
-  <si>
-    <t>行级占位符写成三个大括号{{{xxx}}}，就只取一次，作为文档级占位符</t>
-  </si>
-  <si>
-    <r>
-      <t>{{{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>打印日期}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>}}</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>{{{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>打印时间</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>}}}</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>{{{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>总条数</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>}}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>}</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>{{{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>总小时</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>}}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>}</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>{{{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>当前组别}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>}}</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>{{{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>当前类别</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>}}}</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>{{{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>当前状态</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>}}}</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>多人记录的取舍：{{姓名}} 会列出全部人员，但工号/性别/部门这类字段只取第一位人员（拼成一串没意义）。请假/加班申请单通常是一人一单，不受影响。</t>
-  </si>
-  <si>
-    <t>注意：</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>记录存储里时间是以 {{时段}}（"08:30-17:00"）整体存的，{{开始}}/{{结束}} 自动解析；</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>填写日期：{{{打印日期}}}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>部门：{{{一级部门}}}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{签名}}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>{{{真实姓名</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>}}}</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>也可指定人员签名</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{{考勤人}}}</t>
-  </si>
-  <si>
-    <t>{{{一级部门领导}}}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{{二级部门领导}}}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>记录对应人员的签名，</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>签名占位符（签名图片文件为.\names下对应姓名的jpg文件）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>设置里面考勤组的相应绑定人员</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>{{{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>考勤人</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>}}}</t>
-    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>类别</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -817,7 +973,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -927,13 +1083,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Segoe UI"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -1120,6 +1269,15 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1147,17 +1305,8 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1496,42 +1645,44 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="11.5" customWidth="1"/>
     <col min="2" max="3" width="15.625" customWidth="1"/>
     <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.875" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="6.375" customWidth="1"/>
+    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="37.5" customHeight="1">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:8" ht="37.5" customHeight="1">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-    </row>
-    <row r="2" spans="1:7" ht="39" customHeight="1">
-      <c r="A2" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-    </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+    </row>
+    <row r="2" spans="1:8" ht="39" customHeight="1">
+      <c r="A2" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+    </row>
+    <row r="3" spans="1:8" ht="30" customHeight="1">
       <c r="A3" s="12" t="s">
         <v>1</v>
       </c>
@@ -1548,69 +1699,77 @@
         <v>5</v>
       </c>
       <c r="F3" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="30" customHeight="1">
+      <c r="A4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" s="15" customFormat="1" ht="26.1" customHeight="1">
+      <c r="A5" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="12" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1">
-      <c r="A4" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" s="15" customFormat="1" ht="26.1" customHeight="1">
-      <c r="A5" s="21" t="s">
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+    </row>
+    <row r="6" spans="1:8" ht="50.25" customHeight="1">
+      <c r="A6" s="17" t="s">
         <v>7</v>
-      </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-    </row>
-    <row r="6" spans="1:7" ht="50.25" customHeight="1">
-      <c r="A6" s="17" t="s">
-        <v>8</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
       <c r="D6" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>106</v>
+      <c r="H6" s="9" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A5:H5"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -1620,445 +1779,488 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{614DADB2-EB97-4A0E-BDF8-782DBB5752E1}">
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.625" customWidth="1"/>
     <col min="3" max="3" width="41.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
+      <c r="A1" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
+      <c r="A3" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.25" thickBot="1">
       <c r="A5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.25" thickBot="1">
       <c r="A6" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.25" thickBot="1">
       <c r="A7" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.25" thickBot="1">
       <c r="A8" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="17.25" thickBot="1">
       <c r="A9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17.25" thickBot="1">
       <c r="A10" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17.25" thickBot="1">
       <c r="A11" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="17.25" thickBot="1">
       <c r="A12" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="17.25" thickBot="1">
       <c r="A13" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="17.25" thickBot="1">
       <c r="A14" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14" s="2"/>
     </row>
     <row r="15" spans="1:3" ht="17.25" thickBot="1">
       <c r="A15" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="C15" s="2"/>
     </row>
     <row r="16" spans="1:3" ht="17.25" thickBot="1">
       <c r="A16" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="17.25" thickBot="1">
       <c r="A17" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="17.25" thickBot="1">
       <c r="A18" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="2" t="s">
+    </row>
+    <row r="19" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A19" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
     </row>
     <row r="20" spans="1:3" ht="17.25" thickBot="1">
       <c r="A20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="17.25" thickBot="1">
       <c r="A21" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="17.25" thickBot="1">
       <c r="A22" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="17.25" thickBot="1">
       <c r="A23" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="17.25" thickBot="1">
       <c r="A24" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="17.25" thickBot="1">
       <c r="A25" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="17.25" thickBot="1">
       <c r="A26" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="17.25" thickBot="1">
       <c r="A27" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A28" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="B28" s="23"/>
-      <c r="C28" s="23"/>
+      <c r="A28" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
     </row>
     <row r="29" spans="1:3" ht="17.25" thickBot="1">
       <c r="A29" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="17.25" thickBot="1">
       <c r="A30" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="17.25" thickBot="1">
       <c r="A31" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="17.25" thickBot="1">
       <c r="A32" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C32" s="2"/>
     </row>
     <row r="33" spans="1:3" ht="17.25" thickBot="1">
       <c r="A33" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C33" s="2"/>
     </row>
     <row r="34" spans="1:3" ht="17.25" thickBot="1">
       <c r="A34" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C34" s="2"/>
     </row>
     <row r="35" spans="1:3" ht="17.25" thickBot="1">
       <c r="A35" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C35" s="2"/>
     </row>
     <row r="36" spans="1:3" ht="17.25" thickBot="1">
       <c r="A36" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C36" s="2"/>
     </row>
     <row r="37" spans="1:3" ht="17.25" thickBot="1">
       <c r="A37" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C37" s="2"/>
     </row>
     <row r="38" spans="1:3" ht="16.5">
-      <c r="A38" s="29" t="s">
-        <v>110</v>
-      </c>
-      <c r="B38" s="23"/>
-      <c r="C38" s="23"/>
+      <c r="A38" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="B38" s="26"/>
+      <c r="C38" s="26"/>
     </row>
     <row r="39" spans="1:3" ht="17.25" thickBot="1">
       <c r="A39" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="B39" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="C39" s="28"/>
+        <v>101</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="C39" s="18" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="40" spans="1:3" ht="17.25" thickBot="1">
       <c r="A40" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="B40" s="30" t="s">
-        <v>105</v>
-      </c>
-      <c r="C40" s="27"/>
+        <v>102</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="C40" s="18" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="41" spans="1:3" ht="17.25" thickBot="1">
       <c r="A41" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="B41" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="C41" s="27"/>
+        <v>109</v>
+      </c>
+      <c r="B41" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C41" s="18" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="42" spans="1:3" ht="17.25" thickBot="1">
       <c r="A42" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="B42" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="C42" s="27"/>
+        <v>110</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C42" s="18" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="43" spans="1:3" ht="17.25" thickBot="1">
       <c r="A43" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="B43" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C43" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="B43" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="C43" s="27"/>
-    </row>
-    <row r="44" spans="1:3" ht="39" customHeight="1">
-      <c r="A44" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="B44" s="11"/>
-      <c r="C44" s="11"/>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45">
+    </row>
+    <row r="44" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A44" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B44" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C44" s="20" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A45" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="B45" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C45" s="20" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A46" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C46" s="20" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="39" customHeight="1">
+      <c r="A47" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B47" s="11"/>
+      <c r="C47" s="11"/>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48">
         <v>1</v>
       </c>
-      <c r="B45" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="C45" s="22"/>
-    </row>
-    <row r="46" spans="1:3" ht="48" customHeight="1">
-      <c r="A46">
+      <c r="B48" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="C48" s="25"/>
+    </row>
+    <row r="49" spans="1:3" ht="48" customHeight="1">
+      <c r="A49">
         <v>2</v>
       </c>
-      <c r="B46" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="C46" s="22"/>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47">
+      <c r="B49" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="C49" s="25"/>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50">
         <v>3</v>
       </c>
-      <c r="B47" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="C47" s="22"/>
+      <c r="B50" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="C50" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A3:C3"/>

--- a/source/kaoqing/template/加班申请单模板.xlsx
+++ b/source/kaoqing/template/加班申请单模板.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\小红叔\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{260762A0-98B4-42B2-8628-616EA570D927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0BDC11A-71DC-4CB8-99A1-01D2D94CDE2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9E8CE971-05BC-4D55-8DB8-534D7FFB8A75}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9E8CE971-05BC-4D55-8DB8-534D7FFB8A75}"/>
   </bookViews>
   <sheets>
     <sheet name="template" sheetId="1" r:id="rId1"/>
@@ -1218,7 +1218,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1307,6 +1307,12 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1756,20 +1762,21 @@
         <v>8</v>
       </c>
       <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="14" t="s">
+      <c r="F6" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="G6" s="31"/>
+      <c r="H6" s="32" t="s">
         <v>115</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="E2:H2"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="F6:G6"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/source/kaoqing/template/加班申请单模板.xlsx
+++ b/source/kaoqing/template/加班申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0BDC11A-71DC-4CB8-99A1-01D2D94CDE2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{394F6136-8B86-4D51-8395-EC726E8E636A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9E8CE971-05BC-4D55-8DB8-534D7FFB8A75}"/>
   </bookViews>
@@ -1218,7 +1218,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1290,6 +1290,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1307,12 +1310,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1762,11 +1759,11 @@
         <v>8</v>
       </c>
       <c r="E6" s="9"/>
-      <c r="F6" s="31" t="s">
+      <c r="F6" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="31"/>
-      <c r="H6" s="32" t="s">
+      <c r="G6" s="25"/>
+      <c r="H6" s="17" t="s">
         <v>115</v>
       </c>
     </row>
@@ -1795,18 +1792,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="3" t="s">
@@ -1970,11 +1967,11 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A19" s="26" t="s">
+      <c r="A19" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
     </row>
     <row r="20" spans="1:3" ht="17.25" thickBot="1">
       <c r="A20" s="3" t="s">
@@ -2041,11 +2038,11 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A28" s="26" t="s">
+      <c r="A28" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="B28" s="26"/>
-      <c r="C28" s="26"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="27"/>
     </row>
     <row r="29" spans="1:3" ht="17.25" thickBot="1">
       <c r="A29" s="3" t="s">
@@ -2135,11 +2132,11 @@
       <c r="C37" s="2"/>
     </row>
     <row r="38" spans="1:3" ht="16.5">
-      <c r="A38" s="30" t="s">
+      <c r="A38" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="B38" s="26"/>
-      <c r="C38" s="26"/>
+      <c r="B38" s="27"/>
+      <c r="C38" s="27"/>
     </row>
     <row r="39" spans="1:3" ht="17.25" thickBot="1">
       <c r="A39" s="16" t="s">
@@ -2240,28 +2237,28 @@
       <c r="A48">
         <v>1</v>
       </c>
-      <c r="B48" s="25" t="s">
+      <c r="B48" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="C48" s="25"/>
+      <c r="C48" s="26"/>
     </row>
     <row r="49" spans="1:3" ht="48" customHeight="1">
       <c r="A49">
         <v>2</v>
       </c>
-      <c r="B49" s="25" t="s">
+      <c r="B49" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="C49" s="25"/>
+      <c r="C49" s="26"/>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
         <v>3</v>
       </c>
-      <c r="B50" s="25" t="s">
+      <c r="B50" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="C50" s="25"/>
+      <c r="C50" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/source/kaoqing/template/加班申请单模板.xlsx
+++ b/source/kaoqing/template/加班申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{394F6136-8B86-4D51-8395-EC726E8E636A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{914654C2-63E8-4789-B921-F3B958713392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9E8CE971-05BC-4D55-8DB8-534D7FFB8A75}"/>
   </bookViews>
@@ -1218,7 +1218,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1310,6 +1310,9 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1763,7 +1766,7 @@
         <v>9</v>
       </c>
       <c r="G6" s="25"/>
-      <c r="H6" s="17" t="s">
+      <c r="H6" s="32" t="s">
         <v>115</v>
       </c>
     </row>

--- a/source/kaoqing/template/加班申请单模板.xlsx
+++ b/source/kaoqing/template/加班申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{914654C2-63E8-4789-B921-F3B958713392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D70B3C6C-5B57-4C9C-9582-1D4675A3CE2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9E8CE971-05BC-4D55-8DB8-534D7FFB8A75}"/>
   </bookViews>
@@ -1218,7 +1218,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1290,9 +1290,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1312,7 +1309,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1657,9 +1654,11 @@
     <col min="1" max="1" width="11.5" customWidth="1"/>
     <col min="2" max="3" width="15.625" customWidth="1"/>
     <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.875" customWidth="1"/>
-    <col min="6" max="7" width="6.375" customWidth="1"/>
+    <col min="5" max="5" width="23.125" customWidth="1"/>
+    <col min="6" max="6" width="8.5" customWidth="1"/>
+    <col min="7" max="7" width="9" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="37.5" customHeight="1">
@@ -1762,25 +1761,23 @@
         <v>8</v>
       </c>
       <c r="E6" s="9"/>
-      <c r="F6" s="25" t="s">
+      <c r="G6" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="25"/>
-      <c r="H6" s="32" t="s">
+      <c r="H6" s="9" t="s">
         <v>115</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="E2:H2"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="F6:G6"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="11" scale="82" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="11" scale="75" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1795,18 +1792,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="3" t="s">
@@ -1970,11 +1967,11 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
     </row>
     <row r="20" spans="1:3" ht="17.25" thickBot="1">
       <c r="A20" s="3" t="s">
@@ -2041,11 +2038,11 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A28" s="27" t="s">
+      <c r="A28" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
     </row>
     <row r="29" spans="1:3" ht="17.25" thickBot="1">
       <c r="A29" s="3" t="s">
@@ -2135,11 +2132,11 @@
       <c r="C37" s="2"/>
     </row>
     <row r="38" spans="1:3" ht="16.5">
-      <c r="A38" s="31" t="s">
+      <c r="A38" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="B38" s="27"/>
-      <c r="C38" s="27"/>
+      <c r="B38" s="26"/>
+      <c r="C38" s="26"/>
     </row>
     <row r="39" spans="1:3" ht="17.25" thickBot="1">
       <c r="A39" s="16" t="s">
@@ -2240,28 +2237,28 @@
       <c r="A48">
         <v>1</v>
       </c>
-      <c r="B48" s="26" t="s">
+      <c r="B48" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="C48" s="26"/>
+      <c r="C48" s="25"/>
     </row>
     <row r="49" spans="1:3" ht="48" customHeight="1">
       <c r="A49">
         <v>2</v>
       </c>
-      <c r="B49" s="26" t="s">
+      <c r="B49" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="C49" s="26"/>
+      <c r="C49" s="25"/>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
         <v>3</v>
       </c>
-      <c r="B50" s="26" t="s">
+      <c r="B50" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="C50" s="26"/>
+      <c r="C50" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/source/kaoqing/template/加班申请单模板.xlsx
+++ b/source/kaoqing/template/加班申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D70B3C6C-5B57-4C9C-9582-1D4675A3CE2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1B51D2-BBB8-4639-81F8-72C925928FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9E8CE971-05BC-4D55-8DB8-534D7FFB8A75}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="122">
   <si>
     <t>加班申请单</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -964,6 +964,66 @@
   <si>
     <t>类别</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>岗位职别</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>}}</t>
+    </r>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{{{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>岗位职别</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">}}} </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>也能用</t>
+    </r>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -973,7 +1033,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1084,6 +1144,12 @@
       <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1218,7 +1284,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1278,6 +1344,9 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1309,7 +1378,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1662,30 +1734,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="37.5" customHeight="1">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" ht="39" customHeight="1">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="21" t="s">
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
     </row>
     <row r="3" spans="1:8" ht="30" customHeight="1">
       <c r="A3" s="12" t="s">
@@ -1740,16 +1812,16 @@
       </c>
     </row>
     <row r="5" spans="1:8" s="15" customFormat="1" ht="26.1" customHeight="1">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
     </row>
     <row r="6" spans="1:8" ht="50.25" customHeight="1">
       <c r="A6" s="17" t="s">
@@ -1761,10 +1833,10 @@
         <v>8</v>
       </c>
       <c r="E6" s="9"/>
-      <c r="G6" s="31" t="s">
+      <c r="G6" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="32" t="s">
         <v>115</v>
       </c>
     </row>
@@ -1783,7 +1855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{614DADB2-EB97-4A0E-BDF8-782DBB5752E1}">
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
@@ -1792,18 +1864,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="3" t="s">
@@ -1967,11 +2039,11 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A19" s="26" t="s">
+      <c r="A19" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
     </row>
     <row r="20" spans="1:3" ht="17.25" thickBot="1">
       <c r="A20" s="3" t="s">
@@ -2038,11 +2110,11 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A28" s="26" t="s">
+      <c r="A28" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="B28" s="26"/>
-      <c r="C28" s="26"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="27"/>
     </row>
     <row r="29" spans="1:3" ht="17.25" thickBot="1">
       <c r="A29" s="3" t="s">
@@ -2131,30 +2203,28 @@
       </c>
       <c r="C37" s="2"/>
     </row>
-    <row r="38" spans="1:3" ht="16.5">
-      <c r="A38" s="30" t="s">
+    <row r="38" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A38" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="B38" s="16"/>
+      <c r="C38" s="33" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="16.5">
+      <c r="A39" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="B38" s="26"/>
-      <c r="C38" s="26"/>
-    </row>
-    <row r="39" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A39" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="B39" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="C39" s="18" t="s">
-        <v>108</v>
-      </c>
+      <c r="B39" s="27"/>
+      <c r="C39" s="27"/>
     </row>
     <row r="40" spans="1:3" ht="17.25" thickBot="1">
       <c r="A40" s="16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C40" s="18" t="s">
         <v>108</v>
@@ -2162,10 +2232,10 @@
     </row>
     <row r="41" spans="1:3" ht="17.25" thickBot="1">
       <c r="A41" s="16" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C41" s="18" t="s">
         <v>108</v>
@@ -2173,7 +2243,7 @@
     </row>
     <row r="42" spans="1:3" ht="17.25" thickBot="1">
       <c r="A42" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B42" s="19" t="s">
         <v>105</v>
@@ -2184,7 +2254,7 @@
     </row>
     <row r="43" spans="1:3" ht="17.25" thickBot="1">
       <c r="A43" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B43" s="19" t="s">
         <v>105</v>
@@ -2195,18 +2265,18 @@
     </row>
     <row r="44" spans="1:3" ht="17.25" thickBot="1">
       <c r="A44" s="16" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B44" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="C44" s="20" t="s">
-        <v>114</v>
+      <c r="C44" s="18" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="17.25" thickBot="1">
       <c r="A45" s="16" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="B45" s="19" t="s">
         <v>105</v>
@@ -2217,7 +2287,7 @@
     </row>
     <row r="46" spans="1:3" ht="17.25" thickBot="1">
       <c r="A46" s="16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B46" s="19" t="s">
         <v>105</v>
@@ -2226,50 +2296,61 @@
         <v>114</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="39" customHeight="1">
-      <c r="A47" s="10" t="s">
+    <row r="47" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A47" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="B47" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C47" s="20" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="39" customHeight="1">
+      <c r="A48" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="B47" s="11"/>
-      <c r="C47" s="11"/>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48">
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49">
         <v>1</v>
       </c>
-      <c r="B48" s="25" t="s">
+      <c r="B49" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="C48" s="25"/>
-    </row>
-    <row r="49" spans="1:3" ht="48" customHeight="1">
-      <c r="A49">
+      <c r="C49" s="26"/>
+    </row>
+    <row r="50" spans="1:3" ht="48" customHeight="1">
+      <c r="A50">
         <v>2</v>
       </c>
-      <c r="B49" s="25" t="s">
+      <c r="B50" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="C49" s="25"/>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50">
+      <c r="C50" s="26"/>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51">
         <v>3</v>
       </c>
-      <c r="B50" s="25" t="s">
+      <c r="B51" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="C50" s="25"/>
+      <c r="C51" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="B48:C48"/>
     <mergeCell ref="B49:C49"/>
     <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A39:C39"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/source/kaoqing/template/加班申请单模板.xlsx
+++ b/source/kaoqing/template/加班申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1B51D2-BBB8-4639-81F8-72C925928FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB6ACFC-5626-4E4A-8917-01FE53BEB75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9E8CE971-05BC-4D55-8DB8-534D7FFB8A75}"/>
   </bookViews>
@@ -724,10 +724,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>填写日期：{{{打印日期}}}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>部门：{{{一级部门}}}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1024,6 +1020,10 @@
       <t>也能用</t>
     </r>
     <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>打印时间：{{{打印日期}}} {{{打印时间}}}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1347,6 +1347,12 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1376,12 +1382,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1734,30 +1734,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="37.5" customHeight="1">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:8" ht="39" customHeight="1">
-      <c r="A2" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="22" t="s">
+      <c r="A2" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
     </row>
     <row r="3" spans="1:8" ht="30" customHeight="1">
       <c r="A3" s="12" t="s">
@@ -1776,10 +1776,10 @@
         <v>5</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H3" s="12" t="s">
         <v>69</v>
@@ -1802,7 +1802,7 @@
         <v>41</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>68</v>
@@ -1812,16 +1812,16 @@
       </c>
     </row>
     <row r="5" spans="1:8" s="15" customFormat="1" ht="26.1" customHeight="1">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
     </row>
     <row r="6" spans="1:8" ht="50.25" customHeight="1">
       <c r="A6" s="17" t="s">
@@ -1836,8 +1836,8 @@
       <c r="G6" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="32" t="s">
-        <v>115</v>
+      <c r="H6" s="22" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -1864,18 +1864,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="3" t="s">
@@ -2007,7 +2007,7 @@
     </row>
     <row r="16" spans="1:3" ht="17.25" thickBot="1">
       <c r="A16" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>45</v>
@@ -2039,11 +2039,11 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
     </row>
     <row r="20" spans="1:3" ht="17.25" thickBot="1">
       <c r="A20" s="3" t="s">
@@ -2110,11 +2110,11 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A28" s="27" t="s">
+      <c r="A28" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
     </row>
     <row r="29" spans="1:3" ht="17.25" thickBot="1">
       <c r="A29" s="3" t="s">
@@ -2205,106 +2205,106 @@
     </row>
     <row r="38" spans="1:3" ht="17.25" thickBot="1">
       <c r="A38" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="B38" s="16"/>
+      <c r="C38" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="B38" s="16"/>
-      <c r="C38" s="33" t="s">
-        <v>121</v>
-      </c>
     </row>
     <row r="39" spans="1:3" ht="16.5">
-      <c r="A39" s="31" t="s">
-        <v>107</v>
-      </c>
-      <c r="B39" s="27"/>
-      <c r="C39" s="27"/>
+      <c r="A39" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="B39" s="29"/>
+      <c r="C39" s="29"/>
     </row>
     <row r="40" spans="1:3" ht="17.25" thickBot="1">
       <c r="A40" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="17.25" thickBot="1">
       <c r="A41" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="B41" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="B41" s="19" t="s">
-        <v>103</v>
-      </c>
       <c r="C41" s="18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="17.25" thickBot="1">
       <c r="A42" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="17.25" thickBot="1">
       <c r="A43" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="17.25" thickBot="1">
       <c r="A44" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="17.25" thickBot="1">
       <c r="A45" s="16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="17.25" thickBot="1">
       <c r="A46" s="16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="17.25" thickBot="1">
       <c r="A47" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="B47" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="C47" s="20" t="s">
         <v>113</v>
-      </c>
-      <c r="B47" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="C47" s="20" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="39" customHeight="1">
@@ -2318,28 +2318,28 @@
       <c r="A49">
         <v>1</v>
       </c>
-      <c r="B49" s="26" t="s">
+      <c r="B49" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="C49" s="26"/>
+      <c r="C49" s="28"/>
     </row>
     <row r="50" spans="1:3" ht="48" customHeight="1">
       <c r="A50">
         <v>2</v>
       </c>
-      <c r="B50" s="26" t="s">
+      <c r="B50" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="C50" s="26"/>
+      <c r="C50" s="28"/>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
         <v>3</v>
       </c>
-      <c r="B51" s="26" t="s">
+      <c r="B51" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="C51" s="26"/>
+      <c r="C51" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/source/kaoqing/template/加班申请单模板.xlsx
+++ b/source/kaoqing/template/加班申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB6ACFC-5626-4E4A-8917-01FE53BEB75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCC6400A-1ADC-482F-926F-148AFE1D074D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9E8CE971-05BC-4D55-8DB8-534D7FFB8A75}"/>
   </bookViews>
@@ -984,7 +984,7 @@
       </rPr>
       <t>}}</t>
     </r>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1019,7 +1019,7 @@
       </rPr>
       <t>也能用</t>
     </r>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>打印时间：{{{打印日期}}} {{{打印时间}}}</t>
@@ -1101,42 +1101,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="22"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1148,6 +1116,38 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -1284,7 +1284,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1303,68 +1303,28 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1380,8 +1340,45 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1717,139 +1714,139 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9121F72-ABE7-46BB-8872-B90F12B582AD}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="11.5" customWidth="1"/>
-    <col min="2" max="3" width="15.625" customWidth="1"/>
-    <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.125" customWidth="1"/>
-    <col min="6" max="6" width="8.5" customWidth="1"/>
-    <col min="7" max="7" width="9" customWidth="1"/>
-    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.875" customWidth="1"/>
+    <col min="2" max="2" width="10.5" customWidth="1"/>
+    <col min="3" max="3" width="11.625" customWidth="1"/>
+    <col min="4" max="4" width="7" customWidth="1"/>
+    <col min="5" max="5" width="22.25" customWidth="1"/>
+    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.625" customWidth="1"/>
     <col min="9" max="9" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="37.5" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
     </row>
     <row r="2" spans="1:8" ht="39" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="24" t="s">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
     </row>
     <row r="3" spans="1:8" ht="30" customHeight="1">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="22" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="30" customHeight="1">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="23" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:8" s="15" customFormat="1" ht="26.1" customHeight="1">
-      <c r="A5" s="27" t="s">
+    <row r="5" spans="1:8" s="8" customFormat="1" ht="26.1" customHeight="1">
+      <c r="A5" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-    </row>
-    <row r="6" spans="1:8" ht="50.25" customHeight="1">
-      <c r="A6" s="17" t="s">
+      <c r="B5" s="26"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+    </row>
+    <row r="6" spans="1:8" ht="41.25" customHeight="1">
+      <c r="A6" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="14" t="s">
+      <c r="B6" s="28"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="9"/>
-      <c r="G6" s="21" t="s">
+      <c r="E6" s="28"/>
+      <c r="F6" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="22" t="s">
+      <c r="G6" s="32"/>
+      <c r="H6" s="30" t="s">
         <v>114</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="E2:H2"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="F6:G6"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="11" scale="75" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="11" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1864,18 +1861,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="3" t="s">
@@ -2039,11 +2036,11 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A19" s="29" t="s">
+      <c r="A19" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="29"/>
-      <c r="C19" s="29"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
     </row>
     <row r="20" spans="1:3" ht="17.25" thickBot="1">
       <c r="A20" s="3" t="s">
@@ -2110,11 +2107,11 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="B28" s="29"/>
-      <c r="C28" s="29"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
     </row>
     <row r="29" spans="1:3" ht="17.25" thickBot="1">
       <c r="A29" s="3" t="s">
@@ -2204,142 +2201,142 @@
       <c r="C37" s="2"/>
     </row>
     <row r="38" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A38" s="16" t="s">
+      <c r="A38" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B38" s="16"/>
-      <c r="C38" s="23" t="s">
+      <c r="B38" s="9"/>
+      <c r="C38" s="13" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="16.5">
-      <c r="A39" s="33" t="s">
+      <c r="A39" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="B39" s="29"/>
-      <c r="C39" s="29"/>
+      <c r="B39" s="15"/>
+      <c r="C39" s="15"/>
     </row>
     <row r="40" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A40" s="16" t="s">
+      <c r="A40" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B40" s="19" t="s">
+      <c r="B40" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C40" s="18" t="s">
+      <c r="C40" s="10" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A41" s="16" t="s">
+      <c r="A41" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="B41" s="19" t="s">
+      <c r="B41" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="C41" s="18" t="s">
+      <c r="C41" s="10" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A42" s="16" t="s">
+      <c r="A42" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B42" s="19" t="s">
+      <c r="B42" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="C42" s="18" t="s">
+      <c r="C42" s="10" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A43" s="16" t="s">
+      <c r="A43" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B43" s="19" t="s">
+      <c r="B43" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="C43" s="18" t="s">
+      <c r="C43" s="10" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A44" s="16" t="s">
+      <c r="A44" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="B44" s="19" t="s">
+      <c r="B44" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="C44" s="18" t="s">
+      <c r="C44" s="10" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A45" s="16" t="s">
+      <c r="A45" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="B45" s="19" t="s">
+      <c r="B45" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="C45" s="20" t="s">
+      <c r="C45" s="12" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A46" s="16" t="s">
+      <c r="A46" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B46" s="19" t="s">
+      <c r="B46" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="C46" s="20" t="s">
+      <c r="C46" s="12" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A47" s="16" t="s">
+      <c r="A47" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="B47" s="19" t="s">
+      <c r="B47" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="C47" s="20" t="s">
+      <c r="C47" s="12" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="39" customHeight="1">
-      <c r="A48" s="10" t="s">
+      <c r="A48" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="B48" s="11"/>
-      <c r="C48" s="11"/>
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
         <v>1</v>
       </c>
-      <c r="B49" s="28" t="s">
+      <c r="B49" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="C49" s="28"/>
+      <c r="C49" s="14"/>
     </row>
     <row r="50" spans="1:3" ht="48" customHeight="1">
       <c r="A50">
         <v>2</v>
       </c>
-      <c r="B50" s="28" t="s">
+      <c r="B50" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="C50" s="28"/>
+      <c r="C50" s="14"/>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
         <v>3</v>
       </c>
-      <c r="B51" s="28" t="s">
+      <c r="B51" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="C51" s="28"/>
+      <c r="C51" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/source/kaoqing/template/加班申请单模板.xlsx
+++ b/source/kaoqing/template/加班申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCC6400A-1ADC-482F-926F-148AFE1D074D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF59FA9-7C3A-4DB2-8818-9264D77C7542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9E8CE971-05BC-4D55-8DB8-534D7FFB8A75}"/>
   </bookViews>
@@ -1325,30 +1325,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1360,9 +1336,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1371,14 +1344,41 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1721,7 +1721,7 @@
     <col min="2" max="2" width="10.5" customWidth="1"/>
     <col min="3" max="3" width="11.625" customWidth="1"/>
     <col min="4" max="4" width="7" customWidth="1"/>
-    <col min="5" max="5" width="22.25" customWidth="1"/>
+    <col min="5" max="5" width="25" customWidth="1"/>
     <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.75" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.625" customWidth="1"/>
@@ -1729,110 +1729,110 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="37.5" customHeight="1">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-    </row>
-    <row r="2" spans="1:8" ht="39" customHeight="1">
-      <c r="A2" s="20" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+    </row>
+    <row r="2" spans="1:8" ht="20.25" customHeight="1">
+      <c r="A2" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="21" t="s">
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
     </row>
     <row r="3" spans="1:8" ht="30" customHeight="1">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="14" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="30" customHeight="1">
-      <c r="A4" s="23" t="s">
+    <row r="4" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A4" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="G4" s="25" t="s">
+      <c r="G4" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="H4" s="23" t="s">
+      <c r="H4" s="15" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="8" customFormat="1" ht="26.1" customHeight="1">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
     </row>
     <row r="6" spans="1:8" ht="41.25" customHeight="1">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="29" t="s">
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="28"/>
-      <c r="F6" s="32" t="s">
+      <c r="E6" s="19"/>
+      <c r="F6" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="32"/>
-      <c r="H6" s="30" t="s">
+      <c r="G6" s="23"/>
+      <c r="H6" s="32" t="s">
         <v>114</v>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
     <mergeCell ref="F6:G6"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="11" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
@@ -1861,18 +1861,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="3" t="s">
@@ -2036,11 +2036,11 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
     </row>
     <row r="20" spans="1:3" ht="17.25" thickBot="1">
       <c r="A20" s="3" t="s">
@@ -2107,11 +2107,11 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
     </row>
     <row r="29" spans="1:3" ht="17.25" thickBot="1">
       <c r="A29" s="3" t="s">
@@ -2210,11 +2210,11 @@
       </c>
     </row>
     <row r="39" spans="1:3" ht="16.5">
-      <c r="A39" s="19" t="s">
+      <c r="A39" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="B39" s="15"/>
-      <c r="C39" s="15"/>
+      <c r="B39" s="25"/>
+      <c r="C39" s="25"/>
     </row>
     <row r="40" spans="1:3" ht="17.25" thickBot="1">
       <c r="A40" s="9" t="s">
@@ -2315,28 +2315,28 @@
       <c r="A49">
         <v>1</v>
       </c>
-      <c r="B49" s="14" t="s">
+      <c r="B49" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="C49" s="14"/>
+      <c r="C49" s="24"/>
     </row>
     <row r="50" spans="1:3" ht="48" customHeight="1">
       <c r="A50">
         <v>2</v>
       </c>
-      <c r="B50" s="14" t="s">
+      <c r="B50" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="C50" s="14"/>
+      <c r="C50" s="24"/>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
         <v>3</v>
       </c>
-      <c r="B51" s="14" t="s">
+      <c r="B51" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="C51" s="14"/>
+      <c r="C51" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/source/kaoqing/template/加班申请单模板.xlsx
+++ b/source/kaoqing/template/加班申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF59FA9-7C3A-4DB2-8818-9264D77C7542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A875D3CC-311A-4DE1-BCD6-B2C200ADECC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9E8CE971-05BC-4D55-8DB8-534D7FFB8A75}"/>
   </bookViews>
@@ -1344,9 +1344,18 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1370,15 +1379,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1718,10 +1718,10 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="8.875" customWidth="1"/>
-    <col min="2" max="2" width="10.5" customWidth="1"/>
+    <col min="2" max="2" width="13.5" customWidth="1"/>
     <col min="3" max="3" width="11.625" customWidth="1"/>
-    <col min="4" max="4" width="7" customWidth="1"/>
-    <col min="5" max="5" width="25" customWidth="1"/>
+    <col min="4" max="4" width="7.75" customWidth="1"/>
+    <col min="5" max="5" width="21.25" customWidth="1"/>
     <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.75" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.625" customWidth="1"/>
@@ -1729,30 +1729,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="37.5" customHeight="1">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="30" t="s">
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
     </row>
     <row r="3" spans="1:8" ht="30" customHeight="1">
       <c r="A3" s="14" t="s">
@@ -1807,16 +1807,16 @@
       </c>
     </row>
     <row r="5" spans="1:8" s="8" customFormat="1" ht="26.1" customHeight="1">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
     </row>
     <row r="6" spans="1:8" ht="41.25" customHeight="1">
       <c r="A6" s="18" t="s">
@@ -1828,11 +1828,11 @@
         <v>8</v>
       </c>
       <c r="E6" s="19"/>
-      <c r="F6" s="23" t="s">
+      <c r="F6" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="23"/>
-      <c r="H6" s="32" t="s">
+      <c r="G6" s="26"/>
+      <c r="H6" s="21" t="s">
         <v>114</v>
       </c>
     </row>
@@ -1861,18 +1861,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="3" t="s">
@@ -2036,11 +2036,11 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A19" s="25" t="s">
+      <c r="A19" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
     </row>
     <row r="20" spans="1:3" ht="17.25" thickBot="1">
       <c r="A20" s="3" t="s">
@@ -2107,11 +2107,11 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A28" s="25" t="s">
+      <c r="A28" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="B28" s="25"/>
-      <c r="C28" s="25"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="28"/>
     </row>
     <row r="29" spans="1:3" ht="17.25" thickBot="1">
       <c r="A29" s="3" t="s">
@@ -2210,11 +2210,11 @@
       </c>
     </row>
     <row r="39" spans="1:3" ht="16.5">
-      <c r="A39" s="29" t="s">
+      <c r="A39" s="32" t="s">
         <v>106</v>
       </c>
-      <c r="B39" s="25"/>
-      <c r="C39" s="25"/>
+      <c r="B39" s="28"/>
+      <c r="C39" s="28"/>
     </row>
     <row r="40" spans="1:3" ht="17.25" thickBot="1">
       <c r="A40" s="9" t="s">
@@ -2315,28 +2315,28 @@
       <c r="A49">
         <v>1</v>
       </c>
-      <c r="B49" s="24" t="s">
+      <c r="B49" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="C49" s="24"/>
+      <c r="C49" s="27"/>
     </row>
     <row r="50" spans="1:3" ht="48" customHeight="1">
       <c r="A50">
         <v>2</v>
       </c>
-      <c r="B50" s="24" t="s">
+      <c r="B50" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="C50" s="24"/>
+      <c r="C50" s="27"/>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
         <v>3</v>
       </c>
-      <c r="B51" s="24" t="s">
+      <c r="B51" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="C51" s="24"/>
+      <c r="C51" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/source/kaoqing/template/加班申请单模板.xlsx
+++ b/source/kaoqing/template/加班申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A875D3CC-311A-4DE1-BCD6-B2C200ADECC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F90F15F5-8DF1-4D8A-9E1A-A064B85C3B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9E8CE971-05BC-4D55-8DB8-534D7FFB8A75}"/>
   </bookViews>
@@ -1718,8 +1718,8 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="8.875" customWidth="1"/>
-    <col min="2" max="2" width="13.5" customWidth="1"/>
-    <col min="3" max="3" width="11.625" customWidth="1"/>
+    <col min="2" max="2" width="10.625" customWidth="1"/>
+    <col min="3" max="3" width="14.5" customWidth="1"/>
     <col min="4" max="4" width="7.75" customWidth="1"/>
     <col min="5" max="5" width="21.25" customWidth="1"/>
     <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>

--- a/source/kaoqing/template/加班申请单模板.xlsx
+++ b/source/kaoqing/template/加班申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F90F15F5-8DF1-4D8A-9E1A-A064B85C3B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1381A955-76F1-4C69-A53A-689CB1608349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9E8CE971-05BC-4D55-8DB8-534D7FFB8A75}"/>
   </bookViews>
@@ -1284,7 +1284,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1379,6 +1379,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1793,7 +1796,7 @@
       <c r="D4" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="33" t="s">
         <v>41</v>
       </c>
       <c r="F4" s="15" t="s">

--- a/source/kaoqing/template/加班申请单模板.xlsx
+++ b/source/kaoqing/template/加班申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1381A955-76F1-4C69-A53A-689CB1608349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1193829D-A601-4D7A-BC40-3C0B48CFC765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9E8CE971-05BC-4D55-8DB8-534D7FFB8A75}"/>
   </bookViews>
@@ -1381,7 +1381,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">

--- a/source/kaoqing/template/加班申请单模板.xlsx
+++ b/source/kaoqing/template/加班申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1193829D-A601-4D7A-BC40-3C0B48CFC765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1478B198-348E-4768-8628-3AEEE487A884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9E8CE971-05BC-4D55-8DB8-534D7FFB8A75}"/>
   </bookViews>
@@ -1284,7 +1284,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1325,43 +1325,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1380,8 +1343,49 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1717,7 +1721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9121F72-ABE7-46BB-8872-B90F12B582AD}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="8.875" customWidth="1"/>
@@ -1731,113 +1735,174 @@
     <col min="9" max="9" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="37.5" customHeight="1">
-      <c r="A1" s="23" t="s">
+    <row r="1" spans="1:9" ht="37.5" customHeight="1">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-    </row>
-    <row r="2" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A2" s="24" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="21"/>
+    </row>
+    <row r="2" spans="1:9" ht="20.25" customHeight="1">
+      <c r="A2" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="22" t="s">
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-    </row>
-    <row r="3" spans="1:8" ht="30" customHeight="1">
-      <c r="A3" s="14" t="s">
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="21"/>
+    </row>
+    <row r="3" spans="1:9" ht="30" customHeight="1">
+      <c r="A3" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="24" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A4" s="15" t="s">
+      <c r="I3" s="21"/>
+    </row>
+    <row r="4" spans="1:9" ht="24.95" customHeight="1">
+      <c r="A4" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="E4" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="G4" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="25" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" s="8" customFormat="1" ht="26.1" customHeight="1">
-      <c r="A5" s="25" t="s">
+      <c r="I4" s="21"/>
+    </row>
+    <row r="5" spans="1:9" s="8" customFormat="1" ht="26.1" customHeight="1">
+      <c r="A5" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-    </row>
-    <row r="6" spans="1:8" ht="41.25" customHeight="1">
-      <c r="A6" s="18" t="s">
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="30"/>
+    </row>
+    <row r="6" spans="1:9" ht="41.25" customHeight="1">
+      <c r="A6" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="20" t="s">
+      <c r="B6" s="32"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="19"/>
-      <c r="F6" s="26" t="s">
+      <c r="E6" s="32"/>
+      <c r="F6" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="26"/>
-      <c r="H6" s="21" t="s">
+      <c r="G6" s="34"/>
+      <c r="H6" s="35" t="s">
         <v>114</v>
       </c>
+      <c r="I6" s="21"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="21"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="21"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="21"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="21"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1864,18 +1929,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="3" t="s">
@@ -2039,11 +2104,11 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A19" s="28" t="s">
+      <c r="A19" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
     </row>
     <row r="20" spans="1:3" ht="17.25" thickBot="1">
       <c r="A20" s="3" t="s">
@@ -2110,11 +2175,11 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="B28" s="28"/>
-      <c r="C28" s="28"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
     </row>
     <row r="29" spans="1:3" ht="17.25" thickBot="1">
       <c r="A29" s="3" t="s">
@@ -2213,11 +2278,11 @@
       </c>
     </row>
     <row r="39" spans="1:3" ht="16.5">
-      <c r="A39" s="32" t="s">
+      <c r="A39" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="B39" s="28"/>
-      <c r="C39" s="28"/>
+      <c r="B39" s="15"/>
+      <c r="C39" s="15"/>
     </row>
     <row r="40" spans="1:3" ht="17.25" thickBot="1">
       <c r="A40" s="9" t="s">
@@ -2318,28 +2383,28 @@
       <c r="A49">
         <v>1</v>
       </c>
-      <c r="B49" s="27" t="s">
+      <c r="B49" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="C49" s="27"/>
+      <c r="C49" s="14"/>
     </row>
     <row r="50" spans="1:3" ht="48" customHeight="1">
       <c r="A50">
         <v>2</v>
       </c>
-      <c r="B50" s="27" t="s">
+      <c r="B50" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="C50" s="27"/>
+      <c r="C50" s="14"/>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
         <v>3</v>
       </c>
-      <c r="B51" s="27" t="s">
+      <c r="B51" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="C51" s="27"/>
+      <c r="C51" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/source/kaoqing/template/加班申请单模板.xlsx
+++ b/source/kaoqing/template/加班申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1478B198-348E-4768-8628-3AEEE487A884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C769CBE4-C9B7-4835-A692-99F3259F7091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9E8CE971-05BC-4D55-8DB8-534D7FFB8A75}"/>
   </bookViews>
@@ -1284,7 +1284,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1325,6 +1325,46 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1342,50 +1382,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1721,7 +1717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9121F72-ABE7-46BB-8872-B90F12B582AD}">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="8.875" customWidth="1"/>
@@ -1732,177 +1728,115 @@
     <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.75" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.625" customWidth="1"/>
-    <col min="9" max="9" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="37.5" customHeight="1">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:8" ht="37.5" customHeight="1">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="21"/>
-    </row>
-    <row r="2" spans="1:9" ht="20.25" customHeight="1">
-      <c r="A2" s="22" t="s">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+    </row>
+    <row r="2" spans="1:8" ht="20.25" customHeight="1">
+      <c r="A2" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
       <c r="E2" s="23" t="s">
         <v>121</v>
       </c>
       <c r="F2" s="23"/>
       <c r="G2" s="23"/>
       <c r="H2" s="23"/>
-      <c r="I2" s="21"/>
-    </row>
-    <row r="3" spans="1:9" ht="30" customHeight="1">
-      <c r="A3" s="24" t="s">
+    </row>
+    <row r="3" spans="1:8" ht="30" customHeight="1">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="G3" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="H3" s="24" t="s">
+      <c r="H3" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="I3" s="21"/>
-    </row>
-    <row r="4" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A4" s="25" t="s">
+    </row>
+    <row r="4" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A4" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="F4" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="H4" s="25" t="s">
+      <c r="H4" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="21"/>
-    </row>
-    <row r="5" spans="1:9" s="8" customFormat="1" ht="26.1" customHeight="1">
-      <c r="A5" s="29" t="s">
+    </row>
+    <row r="5" spans="1:8" s="8" customFormat="1" ht="26.1" customHeight="1">
+      <c r="A5" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="30"/>
-    </row>
-    <row r="6" spans="1:9" ht="41.25" customHeight="1">
-      <c r="A6" s="31" t="s">
+      <c r="B5" s="26"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+    </row>
+    <row r="6" spans="1:8" ht="41.25" customHeight="1">
+      <c r="A6" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="32"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="33" t="s">
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="32"/>
-      <c r="F6" s="34" t="s">
+      <c r="E6" s="20"/>
+      <c r="F6" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="34"/>
-      <c r="H6" s="35" t="s">
+      <c r="G6" s="27"/>
+      <c r="H6" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="I6" s="21"/>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="21"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="21"/>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="21"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="21"/>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="21"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="21"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="21"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1929,18 +1863,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="3" t="s">
@@ -2104,11 +2038,11 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
     </row>
     <row r="20" spans="1:3" ht="17.25" thickBot="1">
       <c r="A20" s="3" t="s">
@@ -2175,11 +2109,11 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
     </row>
     <row r="29" spans="1:3" ht="17.25" thickBot="1">
       <c r="A29" s="3" t="s">
@@ -2278,11 +2212,11 @@
       </c>
     </row>
     <row r="39" spans="1:3" ht="16.5">
-      <c r="A39" s="19" t="s">
+      <c r="A39" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="B39" s="15"/>
-      <c r="C39" s="15"/>
+      <c r="B39" s="29"/>
+      <c r="C39" s="29"/>
     </row>
     <row r="40" spans="1:3" ht="17.25" thickBot="1">
       <c r="A40" s="9" t="s">
@@ -2383,28 +2317,28 @@
       <c r="A49">
         <v>1</v>
       </c>
-      <c r="B49" s="14" t="s">
+      <c r="B49" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="C49" s="14"/>
+      <c r="C49" s="28"/>
     </row>
     <row r="50" spans="1:3" ht="48" customHeight="1">
       <c r="A50">
         <v>2</v>
       </c>
-      <c r="B50" s="14" t="s">
+      <c r="B50" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="C50" s="14"/>
+      <c r="C50" s="28"/>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
         <v>3</v>
       </c>
-      <c r="B51" s="14" t="s">
+      <c r="B51" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="C51" s="14"/>
+      <c r="C51" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="8">
